--- a/Intro_files/Semesterplanung.xlsx
+++ b/Intro_files/Semesterplanung.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\ucloud2\Lehre\Personal Coaching Script\PersonalCoaching_Script\Intro_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paedd\OneDrive\Documents\GitHub\PersonalCoaching_Script\Intro_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD2A707-7113-4EB6-A2C7-69DDF586A375}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB61417-F499-4C70-B175-2632439D968F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ECTS" sheetId="5" r:id="rId1"/>
@@ -42,9 +42,6 @@
     <t>Termine Anwesenheit</t>
   </si>
   <si>
-    <t>Supervision</t>
-  </si>
-  <si>
     <t>Reflexion</t>
   </si>
   <si>
@@ -87,24 +84,15 @@
     <t>Reflexion; Präsentationen…. (Breakout)</t>
   </si>
   <si>
-    <t>Für SSA und Abschlussarbeiten gibt es eine klare Null-Toleranz gegenüber Plagiatisierung. Bitte haltet euch gegebenenfalls an Zitierregeln!</t>
-  </si>
-  <si>
     <t>Gesamtpunkte</t>
   </si>
   <si>
-    <t>Aufgrund des dichten Programms und um eine gute Lernatmosphäre zu gewährleisten wird um pünktlichkeit in den Einheiten gebeten.</t>
-  </si>
-  <si>
     <t>Reflexionsarbeit</t>
   </si>
   <si>
     <t>Vorbereitung, Nachbereitung Personal Coaching</t>
   </si>
   <si>
-    <t>Können Anforderungen aus individuellen Gründen nicht erfüllt werden, so liegt es bei den Studierdenden zum fürhest möglichen Zeitpunkt Rücksprache mit der LV-Leitung zu suchen. So kann an eine gemeinsame Lösung gesucht werden</t>
-  </si>
-  <si>
     <t>Durchführen Personal Coaching</t>
   </si>
   <si>
@@ -123,9 +111,6 @@
     <t>Anwesenheitsstunden (siehe Semesterplan)</t>
   </si>
   <si>
-    <t>Anwesenheit 80% muss erfüllt werden</t>
-  </si>
-  <si>
     <t>Krafttraining im PC</t>
   </si>
   <si>
@@ -171,13 +156,28 @@
     <t>Prozent</t>
   </si>
   <si>
-    <t>Durchführen und Doku Supervision</t>
-  </si>
-  <si>
     <t>Peer Review</t>
   </si>
   <si>
     <t>Selbststudiums-Aufgaben (SSA)</t>
+  </si>
+  <si>
+    <t>Hospitation</t>
+  </si>
+  <si>
+    <t>Durchführen und Doku Hospitation</t>
+  </si>
+  <si>
+    <t>Anwesenheit 75% muss erfüllt werden</t>
+  </si>
+  <si>
+    <t>Können Anforderungen aus individuellen Gründen nicht erfüllt werden, so liegt es bei den Studierenden, zum frühestmöglichen Zeitpunkt Rücksprache mit der LV-Leitung zu suchen. So kann an eine gemeinsame Lösung gesucht werden</t>
+  </si>
+  <si>
+    <t>Aufgrund des dichten Programms, und um eine gute Lernatmosphäre zu gewährleisten wird um Pünktlichkeit in den Einheiten gebeten.</t>
+  </si>
+  <si>
+    <t>Für SSA und Abschlussarbeiten gilt eine klare Nulltoleranz gegenüber Plagiatisierung. Bitte haltet euch gegebenenfalls an die Zitierregeln!</t>
   </si>
 </sst>
 </file>
@@ -309,7 +309,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -342,9 +342,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -382,7 +382,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -488,7 +488,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -630,7 +630,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -648,18 +648,18 @@
   <sheetData>
     <row r="1" spans="1:3" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B2" s="9">
         <f>14*1.5</f>
@@ -672,7 +672,7 @@
     </row>
     <row r="3" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="B3" s="9">
         <v>2</v>
@@ -684,7 +684,7 @@
     </row>
     <row r="4" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="9">
         <v>2</v>
@@ -696,7 +696,7 @@
     </row>
     <row r="5" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="9">
         <v>1</v>
@@ -708,7 +708,7 @@
     </row>
     <row r="6" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="9">
         <v>8</v>
@@ -720,7 +720,7 @@
     </row>
     <row r="7" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B7" s="9">
         <v>5</v>
@@ -732,7 +732,7 @@
     </row>
     <row r="8" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B8" s="9">
         <v>12</v>
@@ -744,7 +744,7 @@
     </row>
     <row r="9" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="11">
         <f>SUM(B2:B8)</f>
@@ -774,13 +774,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D1" s="16"/>
     </row>
@@ -789,7 +789,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C2" s="6">
         <v>10</v>
@@ -800,7 +800,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C3" s="6">
         <v>10</v>
@@ -811,7 +811,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C4" s="6">
         <v>10</v>
@@ -822,7 +822,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C5" s="6">
         <v>30</v>
@@ -833,7 +833,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C6" s="6">
         <v>10</v>
@@ -844,7 +844,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C7" s="6">
         <v>30</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" s="5">
         <f>SUM(C2:C7)</f>
@@ -875,13 +875,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -956,7 +956,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="19" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -966,7 +966,7 @@
     </row>
     <row r="2" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -976,7 +976,7 @@
     </row>
     <row r="3" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -986,7 +986,7 @@
     </row>
     <row r="4" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -1004,7 +1004,7 @@
     </row>
     <row r="6" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="18" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="18" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
@@ -1065,7 +1065,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>1.5</v>
@@ -1076,7 +1076,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>1.5</v>
@@ -1087,7 +1087,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4">
         <v>1.5</v>
@@ -1098,7 +1098,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>1.5</v>
@@ -1109,7 +1109,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>1.5</v>
@@ -1120,7 +1120,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>1.5</v>
@@ -1131,7 +1131,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C8">
         <v>1.5</v>
@@ -1142,7 +1142,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C9">
         <v>1.5</v>
@@ -1153,7 +1153,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10">
         <v>1.5</v>
@@ -1164,7 +1164,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11">
         <v>1.5</v>
@@ -1175,7 +1175,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12">
         <v>1.5</v>
@@ -1186,7 +1186,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13">
         <v>1.5</v>
@@ -1197,7 +1197,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>-1.5</v>
@@ -1208,7 +1208,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C15">
         <v>1.5</v>
@@ -1219,7 +1219,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" s="1">
         <v>1.5</v>
